--- a/auto-omega/tuyen-dung-sheet-template.xlsx
+++ b/auto-omega/tuyen-dung-sheet-template.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,7 +39,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF0d5c38"/>
+      <color rgb="FF0D5C38"/>
       <sz val="10"/>
     </font>
     <font>
@@ -85,7 +84,7 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="FF0d5c38"/>
+      <color rgb="FF0D5C38"/>
       <sz val="10"/>
     </font>
     <font>
@@ -94,8 +93,28 @@
       <color rgb="FF1565C0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF212121"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -104,17 +123,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0d5c38"/>
+        <fgColor rgb="FF0D5C38"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8f5e9"/>
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28a745"/>
+        <fgColor rgb="FF28A745"/>
       </patternFill>
     </fill>
     <fill>
@@ -147,8 +166,14 @@
         <fgColor rgb="FFFFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -158,23 +183,50 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,9 +247,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,18 +279,34 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -601,30 +666,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000d5c38"/>
+    <tabColor rgb="FF0D5C38"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" style="19" min="1" max="1"/>
+    <col width="38" customWidth="1" style="19" min="2" max="2"/>
+    <col width="40" customWidth="1" style="19" min="3" max="3"/>
+    <col width="20" customWidth="1" style="19" min="4" max="5"/>
+    <col width="18" customWidth="1" style="19" min="6" max="7"/>
+    <col width="30" customWidth="1" style="19" min="8" max="8"/>
+    <col width="25" customWidth="1" style="19" min="9" max="9"/>
+    <col width="10" customWidth="1" style="19" min="10" max="10"/>
+    <col width="14" customWidth="1" style="19" min="11" max="11"/>
+    <col width="12" customWidth="1" style="19" min="12" max="12"/>
+    <col width="60" customWidth="1" style="19" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.95" customHeight="1" s="19">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Job_ID</t>
@@ -687,16 +749,86 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>Excerpt</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>Role1</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>Role3</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>Role4</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>Role5</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>Require1</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>Require2</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>Require3</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>Require4</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>Require5</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
+        <is>
+          <t>Benefit1</t>
+        </is>
+      </c>
+      <c r="Y1" s="24" t="inlineStr">
+        <is>
+          <t>Benefit2</t>
+        </is>
+      </c>
+      <c r="Z1" s="24" t="inlineStr">
+        <is>
+          <t>Benefit3</t>
+        </is>
+      </c>
+      <c r="AA1" s="24" t="inlineStr">
+        <is>
+          <t>Benefit4</t>
+        </is>
+      </c>
+      <c r="AB1" s="24" t="inlineStr">
+        <is>
+          <t>Benefit5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.95" customHeight="1" s="19">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>J001</t>
@@ -755,16 +887,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Xây dựng và tối ưu hóa hệ thống backend cho nền tảng ERP OMEGA – xử lý nghiệp vụ phức tạp, hiệu năng cao.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Thiết kế và phát triển API (RESTful/GraphQL) phục vụ các phân hệ ERP</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Tối ưu hiệu năng truy vấn CSDL (SQL Server, PostgreSQL)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Tích hợp hệ thống bên thứ ba: thuế điện tử, ngân hàng, EDI</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Review code, hướng dẫn junior developer</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Viết unit/integration test và tài liệu kỹ thuật</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3+ năm kinh nghiệm với .NET (C#) hoặc Node.js</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Thành thạo SQL Server, hiểu ORM (EF Core / Prisma)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Hiểu biết về kiến trúc microservices, REST API</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Có kinh nghiệm ERP / phần mềm quản trị là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Đọc hiểu tài liệu kỹ thuật tiếng Anh</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh + thưởng dự án</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Môi trường Agile, không OT vô tội vạ</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Đào tạo chuyên sâu ERP và công nghệ mới</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch hàng năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.95" customHeight="1" s="19">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>J002</t>
@@ -823,16 +1022,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>Xây dựng giao diện người dùng hiện đại cho hệ thống OMEGA ERP – đẹp, responsive, UX tối ưu.</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Phát triển SPA với Vue 3 / React cho các module ERP</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Xây dựng component library, design system nội bộ</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tối ưu hiệu năng render và bundle size</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Phối hợp Backend và UI/UX hoàn thiện sản phẩm</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Viết unit test cho component</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2+ năm Vue.js hoặc React</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Thành thạo HTML5, CSS3, JavaScript ES2020+</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Có kinh nghiệm TypeScript là lợi thế</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hiểu REST API, Axios, state management (Pinia/Redux)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Portfolio dự án thực tế có thể xem được</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh + review 2 lần/năm</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Làm việc với product dùng thực bởi 1000+ doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Đào tạo UX/UI và công nghệ frontend mới</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, teambuilding, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" s="19">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>J003</t>
@@ -891,16 +1157,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Phát triển ứng dụng mobile cho hệ sinh thái OMEGA (APV, SCR, STK, SOR, MST, HRM App).</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Phát triển tính năng mới cho 6 ứng dụng mobile OMEGA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Tích hợp API với hệ thống ERP backend</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tối ưu hiệu năng trên iOS &amp; Android</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Debug, viết test, phát hành lên App Store / CH Play</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Phối hợp team backend và UI/UX</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2+ năm React Native hoặc Flutter</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Đã publish ít nhất 1 app lên store</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Thành thạo RESTful API, push notification, offline-first</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Có kinh nghiệm barcode/QR scanner là lợi thế</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Biết Git, CI/CD cơ bản</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh, review định kỳ</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Làm việc trực tiếp trên sản phẩm 1000+ doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Đào tạo kỹ thuật, hỗ trợ thi chứng chỉ</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, thưởng dự án</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.95" customHeight="1" s="19">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>J004</t>
@@ -959,16 +1292,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Đảm bảo chất lượng sản phẩm OMEGA ERP – xây dựng test plan, viết test case, automation test.</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Phân tích yêu cầu, lập kế hoạch và thực hiện kiểm thử</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Viết test case, test script cho từng phân hệ ERP</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Xây dựng automation test (Selenium, Playwright hoặc Appium)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Báo cáo lỗi, theo dõi fix trong Jira</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Kiểm thử hiệu năng, bảo mật, hồi quy</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm QA/Testing phần mềm</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kỹ năng viết test case rõ ràng, tư duy kiểm thử tốt</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Biết automation test (Selenium/Playwright) là lợi thế</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Có kiến thức cơ bản về SQL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Cẩn thận, tỉ mỉ, có trách nhiệm với chất lượng</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Lương + thưởng bug bounty</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Đào tạo ISTQB, automation testing</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Môi trường Agile phối hợp trực tiếp dev</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch hàng năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.95" customHeight="1" s="19">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>J005</t>
@@ -1027,16 +1427,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Xây dựng và vận hành hạ tầng cloud, CI/CD pipeline cho hệ thống OMEGA ERP.</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Quản lý hạ tầng cloud (AWS/Azure/GCP) cho ERP</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Xây dựng và tối ưu CI/CD pipeline (GitLab CI, GitHub Actions)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Monitoring, alerting, on-call hạ tầng production</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Containerization (Docker, Kubernetes)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Bảo mật hạ tầng, backup và disaster recovery</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3+ năm kinh nghiệm DevOps/SRE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Thành thạo Linux, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm với ít nhất 1 cloud provider (AWS ưu tiên)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Biết IaC (Terraform/Ansible)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Có chứng chỉ cloud là lợi thế</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh, thưởng vận hành</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Ngân sách cloud và tool hàng năm</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Hỗ trợ thi chứng chỉ AWS/Azure</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, làm việc hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" s="19">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>J006</t>
@@ -1095,16 +1562,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Nghiên cứu và tích hợp AI (LLM, Gemini, GPT) vào hệ sinh thái OMEGA ERP.</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Prototype các tính năng AI cho ERP (chatbot, auto-fill, dự báo)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Tích hợp LLM API (Gemini, OpenAI, Anthropic) vào phân hệ ERP</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Xây dựng AI agent tự động hóa quy trình kế toán, nhân sự</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Đánh giá và tối ưu prompt engineering, RAG pipeline</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Tư vấn kỹ thuật AI cho team triển khai và khách hàng</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3+ năm kinh nghiệm ML/AI hoặc backend với LLM integration</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Thành thạo Python; kinh nghiệm LangChain/LlamaIndex</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hiểu biết về ERP / quản trị doanh nghiệp là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Portfolio dự án AI thực tế</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Đọc hiểu tài liệu kỹ thuật tiếng Anh tốt</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Lương top-market, thưởng nghiên cứu</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Ngân sách API token hàng tháng</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Tham gia hội thảo AI trong và ngoài nước</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Môi trường nghiên cứu tự do</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.95" customHeight="1" s="19">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>J007</t>
@@ -1163,16 +1697,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Tư vấn và triển khai OMEGA ERP tại doanh nghiệp khách hàng – phân tích nghiệp vụ, cấu hình, đào tạo.</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Khảo sát, phân tích quy trình nghiệp vụ của khách hàng</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cấu hình và tùy chỉnh OMEGA ERP theo yêu cầu</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Đào tạo người dùng cuối tại khách hàng</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Hỗ trợ go-live và xử lý sự cố sau triển khai</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Viết tài liệu hướng dẫn sử dụng, quy trình vận hành</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm triển khai ERP hoặc phần mềm quản lý</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Hiểu biết nghiệp vụ kế toán, mua hàng, bán hàng, kho</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Giao tiếp tốt, chịu được áp lực dự án</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Sẵn sàng đi công tác tỉnh thành theo dự án</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH Kế toán, QTKD, CNTT hoặc liên quan</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Lương + phụ cấp công tác</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Đào tạo chuyên sâu toàn bộ hệ thống OMEGA ERP</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Lộ trình thăng tiến lên Team Lead / PM</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch hàng năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.95" customHeight="1" s="19">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>J008</t>
@@ -1231,16 +1832,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>Triển khai phân hệ kế toán OMEGA cho doanh nghiệp – cấu hình đến đào tạo kế toán viên.</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Cấu hình phân hệ GL, FA, MC, CL theo đặc thù khách hàng</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Hỗ trợ nhập số dư đầu kỳ, kiểm tra số liệu</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Đào tạo kế toán viên sử dụng hệ thống</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Xử lý câu hỏi nghiệp vụ kế toán từ khách hàng</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Viết hướng dẫn vận hành, tài liệu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH Kế toán / Kiểm toán / Tài chính</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1+ năm làm kế toán thực tế hoặc triển khai phần mềm kế toán</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hiểu chuẩn mực kế toán VN (VAS, TT200/133)</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Kỹ năng Excel tốt</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Có chứng chỉ kế toán (CPA, ACCA) là lợi thế</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Lương + phụ cấp dự án</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Học nghiệp vụ kế toán từ nhiều ngành</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Hỗ trợ thi chứng chỉ kế toán</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.95" customHeight="1" s="19">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>J009</t>
@@ -1299,16 +1967,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Triển khai phân hệ sản xuất OMEGA cho nhà máy – BOM, lệnh sản xuất, kiểm soát chất lượng.</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Khảo sát quy trình sản xuất tại nhà máy khách hàng</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cấu hình MM (Sản xuất), PC (Giá thành), QC (Chất lượng)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hướng dẫn nhập BOM, routing, lệnh sản xuất</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Đào tạo người dùng nhà máy (quản đốc, kế hoạch, QC)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Xử lý yêu cầu đặc thù ngành</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH kỹ thuật, quản lý sản xuất hoặc kinh tế</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Hiểu biết về quy trình sản xuất, MRP, BOM</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm làm việc trong nhà máy là lợi thế</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Sẵn sàng đi công tác tỉnh theo dự án</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Chịu áp lực, làm việc nhóm tốt</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Lương + phụ cấp công tác hậu hĩnh</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Tiếp xúc đa dạng ngành (nhựa, gỗ, thực phẩm, dệt may)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Đào tạo Lean, ISO, chứng chỉ sản xuất</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, thưởng dự án</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.95" customHeight="1" s="19">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>J010</t>
@@ -1367,16 +2102,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>Triển khai phân hệ nhân sự và tiền lương OMEGA – cấu hình, đào tạo và hỗ trợ sau go-live.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Cấu hình phân hệ HR, Payroll theo đặc thù khách hàng</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Hỗ trợ nhập dữ liệu nhân sự, thiết lập quy tắc tính lương</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Đào tạo bộ phận HR, kế toán lương tại khách hàng</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Xử lý câu hỏi về luật lao động, BHXH trong hệ thống</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Viết tài liệu hướng dẫn sử dụng</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH QTKD, Luật lao động, Kinh tế hoặc CNTT</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Hiểu Luật Lao động VN, BHXH, thuế TNCN</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm HR/C&amp;B hoặc phần mềm nhân sự là lợi thế</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Kỹ năng Excel tốt, tỉ mỉ, cẩn thận</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Giao tiếp tốt, thân thiện với người dùng</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Lương + thưởng dự án</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Nắm vững pháp luật lao động qua thực tế</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Môi trường chuyên nghiệp, teamwork tốt</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.95" customHeight="1" s="19">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>J011</t>
@@ -1435,16 +2237,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Phân tích nghiệp vụ, xây dựng tài liệu yêu cầu – cầu nối giữa khách hàng và team kỹ thuật.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Thu thập và phân tích yêu cầu nghiệp vụ từ doanh nghiệp khách hàng</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Viết BRD, FRD, user story, use case cho các tính năng ERP</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Làm cầu nối giữa khách hàng – triển khai – kỹ thuật</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Tham gia UAT, hỗ trợ kiểm thử nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Đề xuất cải tiến quy trình nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2+ năm kinh nghiệm BA, ưu tiên ERP / phần mềm doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Hiểu biết tốt về quy trình kế toán, sản xuất hoặc nhân sự</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kỹ năng viết tài liệu rõ ràng, chuẩn mực</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Thành thạo BPMN, flowchart, wireframe cơ bản</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tiếng Anh đọc hiểu kỹ thuật tốt</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh + thưởng dự án</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Tiếp xúc đa ngành từ F&amp;B đến y tế, phân phối</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Lộ trình phát triển lên PM hoặc Solution Architect</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, đào tạo chứng chỉ CBAP/PMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.95" customHeight="1" s="19">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>J012</t>
@@ -1503,16 +2372,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>Thiết kế và thực hiện chương trình đào tạo OMEGA ERP cho người dùng cuối.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Soạn giáo trình, slide, video hướng dẫn sử dụng ERP</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Đào tạo trực tiếp và trực tuyến tại khách hàng</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Xây dựng ngân hàng câu hỏi, bài kiểm tra sau đào tạo</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Cập nhật tài liệu khi có phiên bản phần mềm mới</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Hỗ trợ người dùng giai đoạn sau go-live</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Kỹ năng trình bày, giảng dạy tốt</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Hiểu biết cơ bản về kế toán hoặc sản xuất</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Thành thạo PowerPoint, Word, Canva</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sẵn sàng đi tỉnh theo lịch đào tạo</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH bất kỳ ngành</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Lương + phụ cấp đào tạo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Học được nghiệp vụ ERP toàn diện</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Kỹ năng thuyết trình được rèn giũa liên tục</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Bảo hiểm, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.95" customHeight="1" s="19">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>J013</t>
@@ -1571,16 +2507,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Dẫn dắt nhóm triển khai ERP – quản lý dự án, đảm bảo chất lượng và tiến độ.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch và quản lý tiến độ dự án ERP</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Phân công và giám sát công việc nhóm triển khai</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Giải quyết trực tiếp các vấn đề nghiệp vụ phức tạp</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Báo cáo tiến độ cho khách hàng và ban lãnh đạo</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Cải tiến quy trình và phương pháp triển khai</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3+ năm kinh nghiệm triển khai ERP, 1+ năm quản lý nhóm</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Hiểu biết sâu ít nhất 2 phân hệ ERP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kỹ năng lập kế hoạch dự án, quản lý rủi ro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Kỹ năng lãnh đạo, coaching team</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Chứng chỉ PMP / PRINCE2 là lợi thế</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Lương + bonus KPI dự án</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Quyền phê duyệt ngân sách nhóm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Cơ hội phát triển lên PM / Phó GĐ Dịch vụ</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp, xe công tác</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.95" customHeight="1" s="19">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>J014</t>
@@ -1639,16 +2642,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>Tìm kiếm và phát triển khách hàng doanh nghiệp cho OMEGA ERP – thu nhập không giới hạn.</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tìm kiếm, tiếp cận và tư vấn doanh nghiệp về phần mềm ERP</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Demo sản phẩm, xây dựng đề xuất giải pháp phù hợp</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Đàm phán hợp đồng và chốt deal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Chăm sóc, duy trì quan hệ khách hàng</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Phối hợp team triển khai bàn giao dự án</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm bán hàng B2B (phần mềm/dịch vụ là lợi thế lớn)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kỹ năng giao tiếp, thuyết trình, đàm phán tốt</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Chịu được áp lực KPI doanh số</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Có xe máy, sẵn sàng gặp khách hàng ngoài văn phòng</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH bất kỳ chuyên ngành</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Lương cứng + hoa hồng (thu nhập 20–50tr+/tháng nếu đạt KPI)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Đào tạo bán hàng và kiến thức ERP bài bản</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Cơ hội thăng tiến nhanh lên Team Lead / Trưởng phòng</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, teambuilding hàng quý</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21.95" customHeight="1" s="19">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>J015</t>
@@ -1707,16 +2777,78 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Mở rộng thị trường OMEGA ERP tại các ngành mục tiêu và khu vực địa lý mới.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Nghiên cứu và phân tích thị trường, xác định cơ hội tiềm năng</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Xây dựng kế hoạch tiếp cận ngành và khu vực mới</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Phát triển mạng lưới đối tác, đại lý</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Phối hợp marketing tổ chức sự kiện, hội thảo ngành</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Báo cáo phân tích thị trường hàng quý</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2+ năm kinh nghiệm phát triển thị trường B2B</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Có mạng lưới quan hệ doanh nghiệp trong một ngành cụ thể là lợi thế</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kỹ năng phân tích, lập kế hoạch chiến lược</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Thuyết trình tốt, làm việc độc lập và theo nhóm</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Lương + hoa hồng + phụ cấp di chuyển</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Ngân sách phát triển thị trường</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Cơ hội đi công tác trong và ngoài nước</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21.95" customHeight="1" s="19">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>J016</t>
@@ -1775,16 +2907,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>Triển khai chiến lược marketing số cho OMEGA ERP – tăng nhận diện thương hiệu và tạo lead.</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch và triển khai chiến dịch Google Ads, Meta Ads</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Quản lý fanpage Facebook, LinkedIn, YouTube OMEGA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Phân tích dữ liệu GA4, tối ưu conversion rate</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Phối hợp content team tạo nội dung marketing</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Email marketing, nurturing lead theo phễu</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2+ năm kinh nghiệm Digital Marketing B2B</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Thành thạo Google Ads, Meta Ads, Google Analytics 4</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm marketing phần mềm / SaaS là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Kỹ năng phân tích số liệu, tư duy data-driven</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tiếng Anh đọc hiểu marketing tốt</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ngân sách quảng cáo lớn để học hỏi và thử nghiệm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Môi trường sáng tạo, ít báo cáo thủ công</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Review lương 2 lần/năm</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch hàng năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21.95" customHeight="1" s="19">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>J017</t>
@@ -1843,16 +3042,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Tạo nội dung SEO chất lượng cao cho omega.com.vn – tăng organic traffic từ doanh nghiệp.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Nghiên cứu từ khóa, xây dựng kế hoạch nội dung hàng tháng</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Viết bài SEO về ERP, kế toán, quản trị doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tối ưu on-page SEO, internal linking</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Theo dõi ranking, phân tích traffic và cải thiện</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Phối hợp thiết kế tạo infographic, ảnh minh họa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm SEO Content</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kỹ năng viết tiếng Việt tốt, diễn đạt rõ ràng</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hiểu biết cơ bản về kế toán, quản trị doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Biết sử dụng Ahrefs/SEMrush, Google Search Console</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kiên nhẫn, bám sát KPI traffic</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Môi trường học SEO thực chiến với domain uy tín</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Không áp lực bán hàng, tập trung chất lượng nội dung</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Đào tạo kiến thức ERP để viết chuyên sâu</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Bảo hiểm, thưởng khi đạt KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21.95" customHeight="1" s="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>J018</t>
@@ -1911,16 +3177,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>Demo sản phẩm, tư vấn giải pháp và hỗ trợ đội kinh doanh chốt deal ERP.</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Chuẩn bị và thực hiện demo ERP cho khách hàng tiềm năng</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Phân tích yêu cầu sơ bộ, đề xuất giải pháp phù hợp</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Viết đề xuất kỹ thuật, SOW, báo giá</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Hỗ trợ trả lời RFP/RFQ từ doanh nghiệp lớn</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Đào tạo kỹ năng demo cho đội kinh doanh</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3+ năm kinh nghiệm triển khai ERP hoặc pre-sales phần mềm</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Hiểu biết sâu ít nhất 2 phân hệ ERP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kỹ năng trình bày, thuyết phục xuất sắc</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp tốt (có khách hàng FDI)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nắm bắt nhanh yêu cầu nghiệp vụ đa ngành</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Lương cạnh tranh + bonus deal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Tiếp xúc C-level nhiều ngành khác nhau</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Lộ trình lên Solution Architect hoặc Sales Director</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.95" customHeight="1" s="19">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>J019</t>
@@ -1979,16 +3312,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Hỗ trợ kỹ thuật cho 1000+ doanh nghiệp dùng OMEGA ERP – xử lý ticket, debug, hướng dẫn.</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tiếp nhận và xử lý yêu cầu hỗ trợ kỹ thuật từ khách hàng</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Phân loại, ưu tiên và escalate ticket theo quy trình</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Debug lỗi ứng dụng, hướng dẫn khắc phục</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cập nhật knowledge base, FAQ</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Hỗ trợ qua điện thoại, email, Zalo, TeamViewer</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp CĐ/ĐH CNTT hoặc liên quan</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Hiểu biết cơ bản về phần mềm kế toán / ERP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kỹ năng giao tiếp điện thoại tốt, kiên nhẫn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Biết SQL cơ bản để kiểm tra dữ liệu là lợi thế</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tư duy logic, xử lý vấn đề tốt</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Làm việc giờ hành chính, không ca đêm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Học kiến thức ERP toàn diện từ thực tế</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Môi trường team vui vẻ, chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21.95" customHeight="1" s="19">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>J020</t>
@@ -2047,16 +3447,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>Hỗ trợ khách hàng về nghiệp vụ kế toán, nhân sự, sản xuất trong vận hành OMEGA ERP.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tư vấn nghiệp vụ kế toán, thuế, nhân sự qua hệ thống ERP</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Hướng dẫn xử lý tình huống nghiệp vụ phát sinh</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Cập nhật quy định pháp luật vào tài liệu hướng dẫn</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Phối hợp team triển khai xử lý yêu cầu nâng cấp</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Tổng hợp phản hồi khách hàng để cải tiến sản phẩm</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH Kế toán/Kinh tế hoặc liên quan</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Hiểu TT133 hoặc TT200, luật thuế, BHXH</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kỹ năng giao tiếp, viết hướng dẫn rõ ràng</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Kiên nhẫn, tận tâm với khách hàng</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm làm kế toán thực tế là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Học nghiệp vụ từ hàng trăm khách hàng đa ngành</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Không áp lực doanh số</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Môi trường chuyên nghiệp, đội nhóm hỗ trợ tốt</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21.95" customHeight="1" s="19">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>J021</t>
@@ -2115,16 +3582,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Chăm sóc và duy trì mối quan hệ khách hàng dùng OMEGA ERP – tăng retention và upsell.</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Chủ động gọi điện, email chăm sóc khách hàng định kỳ</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Thu thập phản hồi, đánh giá mức độ hài lòng</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Phối hợp xử lý khiếu nại, đảm bảo trải nghiệm tốt</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Tư vấn gia hạn bảo trì, nâng cấp phần mềm</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Cập nhật thông tin khách hàng vào CRM</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH bất kỳ ngành</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kỹ năng giao tiếp điện thoại và email tốt</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Thái độ tích cực, lấy khách hàng làm trung tâm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Chịu được áp lực và thích nghi nhanh</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Biết CRM phần mềm là lợi thế</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Môi trường thân thiện, teamwork tốt</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Đào tạo kỹ năng CSKH chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Cơ hội phát triển lên senior CSKH hoặc kinh doanh</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Bảo hiểm, thưởng chỉ tiêu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21.95" customHeight="1" s="19">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>J022</t>
@@ -2183,16 +3717,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M23" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>Quản lý end-to-end dự án triển khai ERP cho doanh nghiệp – từ kick-off đến go-live.</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch, theo dõi tiến độ và quản lý ngân sách dự án</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Điều phối nguồn lực nội bộ và bên khách hàng</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Quản lý rủi ro và xử lý thay đổi phạm vi dự án</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Báo cáo tiến độ cho ban giám đốc và C-level khách hàng</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Đảm bảo chất lượng và sự hài lòng của khách hàng</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4+ năm kinh nghiệm quản lý dự án phần mềm, ưu tiên ERP</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Chứng chỉ PMP / PRINCE2 là bắt buộc (hoặc cam kết thi 6 tháng)</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hiểu biết sâu về triển khai ERP ở ít nhất 1 ngành</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Kỹ năng lãnh đạo, đàm phán, xử lý xung đột</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp tốt</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Lương + bonus hoàn thành dự án</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Ngân sách đào tạo và chứng chỉ</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Xe công tác, điện thoại công ty</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21.95" customHeight="1" s="19">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>J023</t>
@@ -2251,16 +3852,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Dẫn dắt team kỹ thuật phát triển OMEGA ERP – technical leadership, kiến trúc, chất lượng code.</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Dẫn dắt team 8–15 kỹ sư (backend/frontend/mobile/QA)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Thiết kế kiến trúc, phê duyệt technical decision</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Code review, mentoring developer</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch sprint, phối hợp PM và BA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Nghiên cứu công nghệ mới, định hướng tech stack</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>5+ năm kinh nghiệm lập trình, 2+ năm tech lead</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Thành thạo .NET/Node.js và SQL Server</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hiểu DDD, clean architecture, microservices</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm Agile/Scrum, Jira</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kỹ năng lãnh đạo, coaching team</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Lương top-market + profit sharing</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Toàn quyền về tech stack và quyết định kỹ thuật</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Ngân sách hiring, tool, cloud</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp cho gia đình</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21.95" customHeight="1" s="19">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>J024</t>
@@ -2319,16 +3987,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>Lãnh đạo phòng kinh doanh OMEGA – chiến lược bán hàng, phát triển đội nhóm, KPI doanh thu.</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Xây dựng chiến lược kinh doanh B2B phần mềm ERP</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Quản lý và phát triển đội ngũ 10–15 chuyên viên kinh doanh</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Thiết lập và theo dõi KPI doanh thu, pipeline</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Trực tiếp tham gia deal lớn, đàm phán hợp đồng</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Phối hợp marketing, pre-sales, triển khai</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>5+ năm kinh nghiệm kinh doanh B2B, 2+ năm quản lý team</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm bán phần mềm / SaaS / ERP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kỹ năng lãnh đạo, xây dựng đội nhóm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Tư duy chiến lược và phân tích dữ liệu bán hàng</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mạng lưới quan hệ doanh nghiệp rộng</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Lương cứng + hoa hồng cá nhân + nhóm (thu nhập không giới hạn)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Xe công tác, điện thoại, ngân sách tiếp khách</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>ESOP theo lộ trình</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe cao cấp, du lịch nước ngoài</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21.95" customHeight="1" s="19">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>J025</t>
@@ -2387,16 +4122,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Định hướng công nghệ và lãnh đạo toàn bộ phòng kỹ thuật OMEGA.</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Định hướng chiến lược công nghệ và roadmap sản phẩm dài hạn</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Quản lý 20–30 kỹ sư (backend, frontend, mobile, QA, DevOps)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Đảm bảo chất lượng, bảo mật và hiệu năng hệ thống</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Phối hợp CEO và C-level về đầu tư công nghệ</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Xây dựng văn hóa kỹ thuật và quy trình engineering</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>8+ năm kinh nghiệm kỹ thuật phần mềm, 3+ năm Tech Director/VP Eng</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm phần mềm doanh nghiệp quy mô lớn</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tầm nhìn chiến lược công nghệ 3–5 năm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Kỹ năng lãnh đạo, thu hút và giữ chân nhân tài kỹ thuật</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tiếng Anh thành thạo</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Lương top-market + equity</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Toàn quyền quyết định công nghệ và hiring</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Ngân sách R&amp;D riêng</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Bảo hiểm cao cấp, cổ phần công ty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21.95" customHeight="1" s="19">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>J026</t>
@@ -2455,16 +4257,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>Đảm nhận công tác kế toán nội bộ của Công ty TNHH Công nghệ và Giải pháp Omega.</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Thực hiện nghiệp vụ kế toán tổng hợp, định khoản chứng từ</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Lập báo cáo tài chính định kỳ (tháng/quý/năm)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kê khai và quyết toán thuế (GTGT, TNCN, TNDN)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Theo dõi công nợ phải thu, phải trả</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Phối hợp kiểm toán nội bộ và bên ngoài</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH Kế toán / Kiểm toán / Tài chính</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm kế toán tổng hợp</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hiểu TT200, luật thuế hiện hành</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Thành thạo Excel; biết OMEGA ERP hoặc MISA là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tỉ mỉ, cẩn thận, bảo mật thông tin tốt</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Dùng OMEGA ERP thực tế, hiểu sản phẩm mình hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Môi trường công ty công nghệ trẻ, chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, thưởng Tết hàng năm</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Review lương theo năng lực</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21.95" customHeight="1" s="19">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>J027</t>
@@ -2523,16 +4392,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M28" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Hỗ trợ công tác hành chính tổng hợp và nhân sự tại Omega.</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Thực hiện công việc hành chính: văn thư, lưu trữ, mua sắm VP</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Hỗ trợ tuyển dụng: đăng tin, sàng lọc hồ sơ, sắp xếp phỏng vấn</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Theo dõi chấm công, nghỉ phép, làm thêm giờ</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Thực hiện thủ tục BHXH, BHYT cho nhân viên</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Tổ chức sự kiện nội bộ, sinh nhật, teambuilding</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Thành thạo Word, Excel, email công việc</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Tháo vát, năng động, thân thiện</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Có kinh nghiệm hành chính / nhân sự là lợi thế</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Sống tại TP.HCM</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tốt nghiệp ĐH bất kỳ ngành</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Môi trường trẻ, vui vẻ, teamwork tốt</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Học hỏi toàn bộ quy trình HR trong công ty công nghệ</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Bảo hiểm đầy đủ, thưởng Tết</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Giờ làm việc linh hoạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21.95" customHeight="1" s="19">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>J028</t>
@@ -2591,16 +4527,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>Chịu trách nhiệm tuyển dụng nhân sự chất lượng cho Omega – IT, triển khai, kinh doanh.</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch tuyển dụng theo nhu cầu các phòng ban</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Đăng tin, tìm kiếm ứng viên qua LinkedIn, TopCV, JobStreet</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sàng lọc hồ sơ, phỏng vấn sơ bộ, tư vấn ứng viên</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Phối hợp quản lý phỏng vấn chuyên sâu</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Quản lý quy trình onboarding nhân viên mới</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2+ năm kinh nghiệm tuyển dụng, ưu tiên tuyển IT / tech</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Có mạng lưới ứng viên CNTT, ERP là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kỹ năng headhunting, khai thác LinkedIn Recruiter</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Giao tiếp tốt, tạo thiện cảm với ứng viên</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sử dụng ATS/CRM tuyển dụng thành thạo</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Bonus tuyển dụng thành công</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Ngân sách job posting và headhunting</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Môi trường HR chuyên nghiệp, đào tạo liên tục</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, du lịch hàng năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21.95" customHeight="1" s="19">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>J029</t>
@@ -2659,16 +4662,83 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Thiết kế giao diện người dùng cho OMEGA ERP và ứng dụng mobile – UX thông minh, UI sạch.</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Nghiên cứu UX, phân tích hành vi người dùng ERP</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Thiết kế wireframe, prototype bằng Figma</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Xây dựng design system và component library</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Phối hợp developer đảm bảo UI triển khai đúng thiết kế</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Thiết kế UI cho cả web app và mobile app</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2+ năm kinh nghiệm UI/UX Design</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Thành thạo Figma, hiểu Design System</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Portfolio thực tế có thể xem được (web app / enterprise app)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm ERP / phần mềm doanh nghiệp là lợi thế lớn</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hiểu HTML/CSS cơ bản để phối hợp developer</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Làm việc trên sản phẩm 1000+ doanh nghiệp dùng thực</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Ngân sách tool design (Figma, Maze, Hotjar)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Môi trường sáng tạo, ý kiến thiết kế được trân trọng</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Bảo hiểm sức khỏe, review lương 2 lần/năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21.95" customHeight="1" s="19">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>J030</t>
@@ -2727,17 +4797,85 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>Thiết kế ấn phẩm truyền thông, marketing và thương hiệu cho OMEGA – digital đến print.</t>
         </is>
       </c>
-    </row>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Thiết kế ấn phẩm marketing: banner, brochure, social media post</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Thiết kế nội dung website, email marketing, landing page</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tạo infographic, icon, illustration cho tài liệu ERP</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Hỗ trợ dựng video ngắn, motion graphic</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Đảm bảo nhất quán nhận diện thương hiệu OMEGA</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1+ năm kinh nghiệm thiết kế đồ họa</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Thành thạo Adobe Illustrator, Photoshop; After Effects là lợi thế</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Portfolio đa dạng (digital + print)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Mắt thẩm mỹ tốt, nắm xu hướng thiết kế</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Làm việc theo deadline, chịu được feedback nhiều vòng</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Môi trường sáng tạo, không ép template cứng nhắc</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Ngân sách Adobe CC, Canva Pro</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Cơ hội làm branding cho thương hiệu ERP uy tín</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Bảo hiểm, thưởng Tết</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>⚠ Lưu ý: Cột Status chỉ nhận giá trị ACTIVE | HOT | CLOSED. Sau khi upload lên Google Sheets, điền SHEET_ID vào tuyen-dung.gs.</t>
         </is>
@@ -2745,7 +4883,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="A33:M33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2754,197 +4892,196 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001565C0"/>
+    <tabColor rgb="FF1565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" style="19" min="1" max="1"/>
+    <col width="22" customWidth="1" style="19" min="2" max="2"/>
+    <col width="10" customWidth="1" style="19" min="3" max="3"/>
+    <col width="40" customWidth="1" style="19" min="4" max="4"/>
+    <col width="25" customWidth="1" style="19" min="5" max="5"/>
+    <col width="30" customWidth="1" style="19" min="6" max="6"/>
+    <col width="16" customWidth="1" style="19" min="7" max="7"/>
+    <col width="50" customWidth="1" style="19" min="8" max="8"/>
+    <col width="60" customWidth="1" style="19" min="9" max="9"/>
+    <col width="10" customWidth="1" style="19" min="10" max="10"/>
+    <col width="80" customWidth="1" style="19" min="11" max="11"/>
+    <col width="60" customWidth="1" style="19" min="12" max="13"/>
+    <col width="20" customWidth="1" style="19" min="14" max="14"/>
+    <col width="18" customWidth="1" style="19" min="15" max="15"/>
+    <col width="60" customWidth="1" style="19" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="27.95" customHeight="1" s="19">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>App_ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Job_ID</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Job_Title</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Full_Name</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>CV_Link</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>CV_Text</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>AI_Score</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>AI_Summary</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>AI_Strengths</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>AI_Gaps</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>AI_Recommendation</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>HR_Status</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>HR_Note</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="21.95" customHeight="1" s="19">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>APP-20260416-001</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>16/04/2026 09:30</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>J001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Lập trình viên Backend (.NET / Node.js)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Nguyễn Văn A</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>nguyenvana@email.com</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>0909123456</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>https://drive.google.com/...</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>(hoặc nội dung CV dán tại đây)</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Ứng viên có kinh nghiệm tốt, phù hợp 82% với yêu cầu vị trí.</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>Kinh nghiệm .NET 4 năm, có dự án ERP thực tế</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Chưa có kinh nghiệm với SQL Server nâng cao</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>Hẹn phỏng vấn tuần tới</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>⚠ Sheet này được điền TỰ ĐỘNG bởi Apps Script (tuyen-dung.gs) khi ứng viên nộp hồ sơ. Không cần sửa thủ công.</t>
         </is>
@@ -2961,320 +5098,334 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0037474F"/>
+    <tabColor rgb="FF37474F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="19" min="1" max="1"/>
+    <col width="60" customWidth="1" style="19" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="27.95" customHeight="1" s="19">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="20.1" customHeight="1" s="19">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>── LLM Configuration ──</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr"/>
-      <c r="C2" s="12" t="inlineStr"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="19">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>LLM_Provider</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Nhà cung cấp AI: Gemini | DeepSeek | Grok</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="4" ht="20.1" customHeight="1" s="19">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>LLM_Model</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>gemini-2.0-flash</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Tên model AI (PRIVATE – không được trả về frontend)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="20.1" customHeight="1" s="19">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>LLM_API_Key</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>API Key của nhà cung cấp AI (PRIVATE – không trả về frontend)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="6" ht="20.1" customHeight="1" s="19">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>LLM_Max_Token</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>2048</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Số token tối đa cho phản hồi AI</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="7" ht="20.1" customHeight="1" s="19">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>── Email Configuration ──</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" s="19">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>HR_Emails</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>hr@omega.com.vn;tuyen-dung@omega.com.vn</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Email HR nhận thông báo – phân cách bằng dấu ; (PRIVATE)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="20.1" customHeight="1" s="19">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Email_From_Name</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>OMEGA HR Team</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Tên hiển thị trong email gửi ra</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="10" ht="20.1" customHeight="1" s="19">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Email_Reply_To</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>hr@omega.com.vn</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Email reply-to cho ứng viên</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="20.1" customHeight="1" s="19">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>── System Settings ──</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" s="19">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Company_Name</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Công ty TNHH Công nghệ và Giải pháp Omega</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Tên công ty đầy đủ</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="20.1" customHeight="1" s="19">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Company_Name_EN</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Omega Solution &amp; Technology Co., Ltd.</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Tên tiếng Anh</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="14" ht="20.1" customHeight="1" s="19">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Company_Website</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>https://omega.com.vn</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Website chính</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="20.1" customHeight="1" s="19">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Min_Score_Pass</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Điểm AI tối thiểu để tự động chuyển trạng thái CONSIDER</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="16" ht="20.1" customHeight="1" s="19">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Auto_Reply_Delay_Hours</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Thời gian tối đa gửi email phản hồi cho ứng viên (giờ)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="20.1" customHeight="1" s="19">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Max_CV_Text_Length</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Giới hạn ký tự cho CV Text paste</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="20.1" customHeight="1" s="19">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>── Security (PRIVATE) ──</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr"/>
-      <c r="C18" s="12" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Master_Password</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Mật khẩu master để reset/override (PRIVATE – không trả về frontend)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="20" ht="20.1" customHeight="1" s="19" thickBot="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Allowed_Origins</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>https://omega.com.vn</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Các domain được phép POST (CORS)</t>
         </is>
       </c>
     </row>
+    <row r="21" ht="15.75" customHeight="1" s="19" thickBot="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Hide_Inactive</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Nếu chọn là ẩn luôn các tin CLOSED và PAUSED</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>🔒 Các dòng màu đỏ nhạt là PRIVATE KEYS – Apps Script sẽ KHÔNG trả về các giá trị này cho frontend HTML.</t>
         </is>
@@ -3293,6 +5444,9 @@
           <t>ℹ️ URL Sheet: https://docs.google.com/spreadsheets/d/{SHEET_ID}/edit</t>
         </is>
       </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3301,5 +5455,6 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>